--- a/data/trans_orig/P1431-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1431-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad de riñón en 2012</t>
+          <t>Población con diagnóstico de enfermedad de riñón en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16946</t>
+          <t>17369</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284897</t>
+          <t>284663</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293770</t>
+          <t>293524</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275942</t>
+          <t>276451</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285314</t>
+          <t>285365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>565037</t>
+          <t>564614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>577208</t>
+          <t>577738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15450</t>
+          <t>14613</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>23772</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491156</t>
+          <t>490726</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502471</t>
+          <t>502477</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>507206</t>
+          <t>508043</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>519568</t>
+          <t>519650</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1005161</t>
+          <t>1004412</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1020016</t>
+          <t>1020020</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8167</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11349</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>315879</t>
+          <t>315705</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>323865</t>
+          <t>323097</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333520</t>
+          <t>333567</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653717</t>
+          <t>653856</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>663068</t>
+          <t>663077</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>11689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5079</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>17739</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23461</t>
+          <t>24955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>362889</t>
+          <t>362293</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372616</t>
+          <t>372894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>371283</t>
+          <t>371212</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383872</t>
+          <t>383873</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>739472</t>
+          <t>737978</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>754886</t>
+          <t>754306</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16329</t>
+          <t>16676</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20289</t>
+          <t>19812</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205265</t>
+          <t>205464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>203262</t>
+          <t>202915</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215633</t>
+          <t>215627</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>411920</t>
+          <t>412397</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426834</t>
+          <t>427015</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14166</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264443</t>
+          <t>263706</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272937</t>
+          <t>272916</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270465</t>
+          <t>270479</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>537911</t>
+          <t>538406</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549051</t>
+          <t>549169</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15625</t>
+          <t>17295</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>21168</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>647163</t>
+          <t>645493</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>659797</t>
+          <t>659890</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>683629</t>
+          <t>684449</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>692827</t>
+          <t>692841</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1334817</t>
+          <t>1335473</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1351436</t>
+          <t>1351414</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16760</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22217</t>
+          <t>20335</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13683</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32092</t>
+          <t>32008</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>762338</t>
+          <t>762694</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>774904</t>
+          <t>774958</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>800361</t>
+          <t>802243</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>815390</t>
+          <t>816138</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1569584</t>
+          <t>1569668</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1587993</t>
+          <t>1587946</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29762</t>
+          <t>29226</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>55431</t>
+          <t>54776</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39194</t>
+          <t>39296</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>68807</t>
+          <t>71483</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,47 +3525,47 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>93968</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>76749</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>115093</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>93968</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>75815</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>116106</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3371348</t>
+          <t>3372003</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3397017</t>
+          <t>3397553</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3485183</t>
+          <t>3482507</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3514796</t>
+          <t>3514694</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,47 +3638,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6415</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6886801</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6865676</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6904020</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>98,9%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6415</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6886801</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6864663</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6904954</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad de riñón en 2016</t>
+          <t>Población con diagnóstico de enfermedad de riñón en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12560</t>
+          <t>12710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20077</t>
+          <t>18221</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283256</t>
+          <t>283172</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292009</t>
+          <t>292030</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>276143</t>
+          <t>275993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286604</t>
+          <t>286478</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>562387</t>
+          <t>564243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>576643</t>
+          <t>577292</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>12881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>12060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6258</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>488452</t>
+          <t>489694</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500354</t>
+          <t>500391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>510333</t>
+          <t>511024</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>520998</t>
+          <t>521020</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1005121</t>
+          <t>1005061</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1019401</t>
+          <t>1019307</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>11730</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311016</t>
+          <t>310740</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329163</t>
+          <t>328843</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643387</t>
+          <t>643144</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653008</t>
+          <t>652875</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14833</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2362</t>
+          <t>2391</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>7937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24103</t>
+          <t>23234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>355131</t>
+          <t>355915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366834</t>
+          <t>366985</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>372811</t>
+          <t>373005</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>384921</t>
+          <t>384892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>733144</t>
+          <t>734013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749162</t>
+          <t>749310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13192</t>
+          <t>12789</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>11312</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18282</t>
+          <t>18549</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198029</t>
+          <t>198432</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209238</t>
+          <t>209243</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207762</t>
+          <t>207275</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217432</t>
+          <t>217399</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>411526</t>
+          <t>411259</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>424579</t>
+          <t>425350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19564</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7779</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22549</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254518</t>
+          <t>254267</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262241</t>
+          <t>262228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253551</t>
+          <t>254823</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>267667</t>
+          <t>267983</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>513689</t>
+          <t>513262</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>528459</t>
+          <t>527866</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>17163</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22316</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>646111</t>
+          <t>645419</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>654620</t>
+          <t>654629</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>674989</t>
+          <t>674131</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>687683</t>
+          <t>687691</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1325536</t>
+          <t>1324791</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1340567</t>
+          <t>1340608</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18485</t>
+          <t>19236</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5946</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21780</t>
+          <t>22539</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14967</t>
+          <t>14485</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35379</t>
+          <t>34987</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>760098</t>
+          <t>759347</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>773470</t>
+          <t>773376</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>804387</t>
+          <t>803628</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>820221</t>
+          <t>819218</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1569371</t>
+          <t>1569763</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1589783</t>
+          <t>1590265</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>33934</t>
+          <t>32698</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59228</t>
+          <t>59689</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43155</t>
+          <t>42479</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>75180</t>
+          <t>74301</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>81547</t>
+          <t>83709</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>123618</t>
+          <t>123584</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3335122</t>
+          <t>3334661</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3360416</t>
+          <t>3361652</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3469362</t>
+          <t>3470241</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3501387</t>
+          <t>3502063</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6815274</t>
+          <t>6815308</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6857345</t>
+          <t>6855183</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1431-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1431-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>11224</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17369</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284663</t>
+          <t>285054</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293524</t>
+          <t>293743</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>276451</t>
+          <t>276021</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285365</t>
+          <t>285357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564614</t>
+          <t>565079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>577738</t>
+          <t>577959</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14801</t>
+          <t>14486</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14613</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23772</t>
+          <t>25188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490726</t>
+          <t>491041</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502477</t>
+          <t>502450</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>508043</t>
+          <t>509050</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>519650</t>
+          <t>519575</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1004412</t>
+          <t>1002996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1020020</t>
+          <t>1020061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>937</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11284</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>315705</t>
+          <t>315171</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>323097</t>
+          <t>323109</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333567</t>
+          <t>333610</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653856</t>
+          <t>653782</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>663077</t>
+          <t>663089</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17739</t>
+          <t>18025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24955</t>
+          <t>23820</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>362293</t>
+          <t>362808</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372894</t>
+          <t>372586</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>371212</t>
+          <t>370926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>383873</t>
+          <t>383918</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>737978</t>
+          <t>739113</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>754306</t>
+          <t>754867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>17059</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5752</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19812</t>
+          <t>20643</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205464</t>
+          <t>205416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>202915</t>
+          <t>202532</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215627</t>
+          <t>215845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>412397</t>
+          <t>411566</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>427015</t>
+          <t>426457</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10285</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>263706</t>
+          <t>263696</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272916</t>
+          <t>272941</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270479</t>
+          <t>270504</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>538406</t>
+          <t>538308</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549169</t>
+          <t>549192</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17295</t>
+          <t>16422</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9404</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>21297</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>645493</t>
+          <t>646366</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>659890</t>
+          <t>660000</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>684449</t>
+          <t>683736</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>692841</t>
+          <t>692819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1335473</t>
+          <t>1335344</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1351414</t>
+          <t>1351467</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6440</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20335</t>
+          <t>22253</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13730</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32008</t>
+          <t>31308</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>762694</t>
+          <t>762190</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>774958</t>
+          <t>774911</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>802243</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>816138</t>
+          <t>815144</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1569668</t>
+          <t>1570368</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1587946</t>
+          <t>1588044</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29226</t>
+          <t>29100</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54776</t>
+          <t>55218</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39296</t>
+          <t>39653</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71483</t>
+          <t>68541</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>76749</t>
+          <t>76676</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>115093</t>
+          <t>115973</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3372003</t>
+          <t>3371561</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3397553</t>
+          <t>3397679</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3482507</t>
+          <t>3485449</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3514694</t>
+          <t>3514337</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6865676</t>
+          <t>6864796</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6904020</t>
+          <t>6904093</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1763</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12710</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18221</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283172</t>
+          <t>283180</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292030</t>
+          <t>291998</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275993</t>
+          <t>276192</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286478</t>
+          <t>286602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564243</t>
+          <t>564356</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>577292</t>
+          <t>577328</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12881</t>
+          <t>13976</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12060</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20598</t>
+          <t>20827</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489694</t>
+          <t>488599</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>500391</t>
+          <t>499553</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>511024</t>
+          <t>511488</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521020</t>
+          <t>521042</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1005061</t>
+          <t>1004832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1019307</t>
+          <t>1019426</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>781</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>12361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310740</t>
+          <t>311255</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317786</t>
+          <t>317784</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328843</t>
+          <t>327730</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643144</t>
+          <t>642513</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652875</t>
+          <t>653140</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2391</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14278</t>
+          <t>14221</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23234</t>
+          <t>23380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>355915</t>
+          <t>355922</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366985</t>
+          <t>367208</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>373005</t>
+          <t>373062</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>384892</t>
+          <t>384281</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>734013</t>
+          <t>733867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>749310</t>
+          <t>749172</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11312</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18549</t>
+          <t>18765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198432</t>
+          <t>198386</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209243</t>
+          <t>209222</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>207275</t>
+          <t>208267</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>217399</t>
+          <t>217398</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>411259</t>
+          <t>411043</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>425350</t>
+          <t>424836</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>8260</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18292</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22976</t>
+          <t>23278</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254267</t>
+          <t>254863</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262228</t>
+          <t>262175</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254823</t>
+          <t>254235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>267983</t>
+          <t>267707</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>513262</t>
+          <t>512960</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>527866</t>
+          <t>528240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11139</t>
+          <t>11068</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17163</t>
+          <t>16246</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23061</t>
+          <t>23029</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>645419</t>
+          <t>645490</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>654629</t>
+          <t>654780</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>674131</t>
+          <t>675048</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>687691</t>
+          <t>687791</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1324791</t>
+          <t>1324823</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1340608</t>
+          <t>1341146</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5207</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19236</t>
+          <t>19019</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22539</t>
+          <t>23373</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14485</t>
+          <t>15134</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34987</t>
+          <t>35234</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>759347</t>
+          <t>759564</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>773376</t>
+          <t>773332</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>803628</t>
+          <t>802794</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>819218</t>
+          <t>819329</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1569763</t>
+          <t>1569516</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1590265</t>
+          <t>1589616</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32698</t>
+          <t>33665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>59689</t>
+          <t>61551</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>42479</t>
+          <t>43202</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74301</t>
+          <t>75001</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6848,42 +6848,42 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>102298</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>83455</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>123761</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>1,2%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>102298</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>83709</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>123584</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3334661</t>
+          <t>3332799</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3361652</t>
+          <t>3360685</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3470241</t>
+          <t>3469541</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3502063</t>
+          <t>3501340</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6961,47 +6961,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6473</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>6836594</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>6815131</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6855437</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>98,22%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>98,8%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6473</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>6836594</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>6815308</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>6855183</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
         </is>
       </c>
     </row>
